--- a/共有管理.xlsx
+++ b/共有管理.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://komazawa-my.sharepoint.com/personal/1mr5187i_komazawa-u_ac_jp/Documents/デスクトップ/土地探し/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_6F34303B88E766335F597915AA4EF4C282D422F8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E63D2BC1-B278-4A85-A3C2-5F9684CA3EDF}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="11_6F34303B88E766335F597915AA4EF4C282D422F8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{15C6762D-161D-45C6-8AF1-30BA26643775}"/>
   <bookViews>
     <workbookView xWindow="4095" yWindow="3750" windowWidth="17280" windowHeight="10665" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="24">
   <si>
     <t>土地探しツール 共有管理シート（詳しい使い方は下の「使い方」タブへ）</t>
   </si>
@@ -84,13 +84,25 @@
   </si>
   <si>
     <t>　　　編集が終わったら必ず保存して閉じてから更新ボタンを押してください。</t>
+  </si>
+  <si>
+    <t>いっしん</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>issin</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>tetuya1234</t>
+    <phoneticPr fontId="5"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -125,6 +137,17 @@
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -172,7 +195,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -181,6 +204,8 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
@@ -495,13 +520,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
     </row>
     <row r="2" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="2" t="s">
@@ -544,8 +569,8 @@
       <c r="B4" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>12</v>
+      <c r="C4" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>9</v>
@@ -553,10 +578,18 @@
       <c r="E4" s="4"/>
     </row>
     <row r="5" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A5" s="4"/>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
+      <c r="A5" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="4">
+        <v>250140</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>9</v>
+      </c>
       <c r="E5" s="4"/>
     </row>
     <row r="6" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
